--- a/diseases/d167/2026-2029.xlsx
+++ b/diseases/d167/2026-2029.xlsx
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN52" t="b">

--- a/diseases/d167/2026-2029.xlsx
+++ b/diseases/d167/2026-2029.xlsx
@@ -6847,12 +6847,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6886,81 +6886,92 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O39" t="n">
-        <v>3</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0.005813909771376137</v>
+        <v>2</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_EARLY_CONGENITAL_SYPHILIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_EARLY_CONGENITAL_SYPHILIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -6987,17 +6998,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -7022,31 +7033,48 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_CA_ON_PHO_IDTO_EARLY_CONGENITAL_SYPHILIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_EARLY_CONGENITAL_SYPHILIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Syphilis, Early Congenital</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -7054,6 +7082,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary early congenital syphilis notifications within two years of birth; confirmed cases only. This source category is narrower than the ontology's all-congenital D167 concept.</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN40" t="b">
+        <v>1</v>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -7071,7 +7157,7 @@
       </c>
       <c r="AS40" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_CA_ON_PHO_IDTO_EARLY_CONGENITAL_SYPHILIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT40" t="n">
@@ -7084,17 +7170,17 @@
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -7104,17 +7190,17 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
@@ -7146,17 +7232,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -7181,179 +7267,90 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>Syphilis congenital</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG41" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Australia NINDSS congenital syphilis notifications.</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN41" t="b">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.005813909771376137</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ41" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -7385,12 +7382,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -7429,33 +7426,50 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS42" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -7465,12 +7479,12 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -7485,12 +7499,12 @@
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
@@ -7522,17 +7536,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -7571,33 +7585,125 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Syphilis congenital</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital syphilis notifications.</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN43" t="b">
+        <v>1</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS43" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -7607,12 +7713,12 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -7627,12 +7733,12 @@
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
@@ -7669,12 +7775,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -7749,7 +7855,7 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -7769,7 +7875,7 @@
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
@@ -7811,12 +7917,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7891,7 +7997,7 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -7911,7 +8017,7 @@
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
@@ -7953,12 +8059,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -8033,7 +8139,7 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -8053,7 +8159,7 @@
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
@@ -8095,12 +8201,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -8175,7 +8281,7 @@
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
@@ -8195,7 +8301,7 @@
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
@@ -8237,12 +8343,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -8317,7 +8423,7 @@
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -8337,7 +8443,7 @@
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
@@ -8379,12 +8485,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -8459,7 +8565,7 @@
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
@@ -8479,7 +8585,7 @@
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
@@ -8521,12 +8627,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -8565,12 +8671,9 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -8599,42 +8702,42 @@
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -8666,12 +8769,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -8696,12 +8799,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8710,50 +8813,33 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ51" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -8763,12 +8849,12 @@
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -8783,12 +8869,12 @@
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
@@ -8820,17 +8906,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8855,12 +8941,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -8869,165 +8955,76 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>Syphilis congenital</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD52" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG52" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Australia NINDSS congenital syphilis notifications.</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN52" t="b">
-        <v>1</v>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ52" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -9059,118 +9056,511 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Syphilis congenital</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital syphilis notifications.</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t>先天性梅毒</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="inlineStr">
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO53" t="inlineStr">
+      <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP53" t="inlineStr">
+      <c r="AP55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR53" t="inlineStr">
+      <c r="AR55" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS53" t="inlineStr"/>
-      <c r="AT53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV53" t="inlineStr">
+      <c r="AV55" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW53" t="inlineStr">
+      <c r="AW55" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
+      <c r="AX55" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY53" t="inlineStr">
+      <c r="AY55" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
+      <c r="AZ55" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA53" t="inlineStr">
+      <c r="BA55" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB53" t="inlineStr">
+      <c r="BB55" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC53" t="inlineStr">
+      <c r="BC55" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -9292,7 +9682,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -9302,7 +9692,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -9322,7 +9712,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -9354,7 +9744,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d167/2026-2029.xlsx
+++ b/diseases/d167/2026-2029.xlsx
@@ -3676,7 +3676,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">

--- a/diseases/d167/2026-2029.xlsx
+++ b/diseases/d167/2026-2029.xlsx
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>0.007345623639039581</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -9254,10 +9254,10 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
@@ -9488,13 +9488,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -9561,6 +9561,151 @@
         </is>
       </c>
       <c r="BC55" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -9599,7 +9744,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9827,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -9692,7 +9837,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
@@ -9744,7 +9889,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d167/2026-2029.xlsx
+++ b/diseases/d167/2026-2029.xlsx
@@ -4064,6 +4064,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7257,6 +7262,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10693,6 +10703,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13886,6 +13901,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17079,6 +17099,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20908,6 +20933,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24980,6 +25010,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28610,12 +28645,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -28654,76 +28689,87 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="R148" t="n">
-        <v>0</v>
-      </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_EARLY_CONGENITAL_SYPHILIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS148" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_EARLY_CONGENITAL_SYPHILIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -28750,17 +28796,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -28785,31 +28831,48 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
-        <v>2</v>
-      </c>
-      <c r="R149" t="n">
-        <v>0.007345623639039581</v>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_CA_ON_PHO_IDTO_EARLY_CONGENITAL_SYPHILIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_EARLY_CONGENITAL_SYPHILIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>Syphilis, Early Congenital</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -28817,6 +28880,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary early congenital syphilis notifications within two years of birth; confirmed cases only. This source category is narrower than the ontology's all-congenital D167 concept.</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN149" t="b">
+        <v>1</v>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -28834,7 +28955,7 @@
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_CA_ON_PHO_IDTO_EARLY_CONGENITAL_SYPHILIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT149" t="n">
@@ -28847,17 +28968,17 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -28867,17 +28988,17 @@
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
@@ -28909,17 +29030,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -28944,48 +29065,26 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
-        <v>2</v>
-      </c>
-      <c r="U150" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
-      <c r="V150" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
-      <c r="W150" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X150" t="inlineStr">
-        <is>
-          <t>Syphilis congenital</t>
-        </is>
-      </c>
-      <c r="Y150" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -28993,130 +29092,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD150" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE150" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF150" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG150" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI150" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Australia NINDSS congenital syphilis notifications.</t>
-        </is>
-      </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN150" t="b">
-        <v>1</v>
-      </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ150" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -29148,12 +29185,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -29187,17 +29224,17 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="U151" t="inlineStr">
@@ -29245,12 +29282,12 @@
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -29265,12 +29302,12 @@
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
@@ -29307,12 +29344,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -29346,10 +29383,10 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U152" t="inlineStr">
         <is>
@@ -29393,7 +29430,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>country:AU-ACT:national</t>
+          <t>country:AU:national</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr">
@@ -29479,12 +29516,12 @@
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -29499,12 +29536,12 @@
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
@@ -29541,12 +29578,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -29579,9 +29616,18 @@
           <t>2026-09</t>
         </is>
       </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="U153" t="inlineStr">
@@ -29596,7 +29642,7 @@
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
@@ -29606,7 +29652,7 @@
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
@@ -29619,7 +29665,7 @@
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
@@ -29629,7 +29675,7 @@
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
@@ -29649,7 +29695,7 @@
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
@@ -29686,17 +29732,17 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -29735,27 +29781,102 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="R154" t="n">
-        <v>0</v>
-      </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="U154" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>Syphilis congenital</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>country:AU-ACT:national</t>
+        </is>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital syphilis notifications.</t>
+        </is>
+      </c>
+      <c r="AM154" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN154" t="b">
+        <v>1</v>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
@@ -29765,7 +29886,7 @@
       </c>
       <c r="AQ154" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
@@ -29778,7 +29899,7 @@
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
@@ -29788,7 +29909,7 @@
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
@@ -29808,7 +29929,7 @@
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
@@ -29845,17 +29966,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -29888,104 +30009,20 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N155" t="n">
-        <v>0</v>
-      </c>
-      <c r="O155" t="n">
-        <v>0</v>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U155" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
-      <c r="V155" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
-      <c r="W155" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X155" t="inlineStr">
-        <is>
-          <t>Syphilis congenital</t>
-        </is>
-      </c>
-      <c r="Y155" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>country:AU-NT:national</t>
-        </is>
-      </c>
-      <c r="AD155" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE155" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF155" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG155" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>Australia NINDSS congenital syphilis notifications.</t>
-        </is>
-      </c>
-      <c r="AM155" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN155" t="b">
-        <v>1</v>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
@@ -30022,7 +30059,7 @@
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
@@ -30042,7 +30079,7 @@
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
@@ -30084,12 +30121,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -30122,9 +30159,18 @@
           <t>2026-09</t>
         </is>
       </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="U156" t="inlineStr">
@@ -30172,7 +30218,7 @@
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
@@ -30192,7 +30238,7 @@
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
@@ -30229,17 +30275,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -30278,23 +30324,98 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="R157" t="n">
-        <v>0</v>
-      </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="U157" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Syphilis congenital</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>country:AU-NT:national</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital syphilis notifications.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN157" t="b">
+        <v>1</v>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
@@ -30331,7 +30452,7 @@
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
@@ -30351,7 +30472,7 @@
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
@@ -30388,17 +30509,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -30431,104 +30552,20 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N158" t="n">
-        <v>0</v>
-      </c>
-      <c r="O158" t="n">
-        <v>0</v>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U158" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
-      <c r="V158" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
-      <c r="W158" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X158" t="inlineStr">
-        <is>
-          <t>Syphilis congenital</t>
-        </is>
-      </c>
-      <c r="Y158" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>country:AU-SA:national</t>
-        </is>
-      </c>
-      <c r="AD158" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE158" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF158" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG158" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ158" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>Australia NINDSS congenital syphilis notifications.</t>
-        </is>
-      </c>
-      <c r="AM158" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN158" t="b">
-        <v>1</v>
       </c>
       <c r="AO158" t="inlineStr">
         <is>
@@ -30565,7 +30602,7 @@
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
@@ -30585,7 +30622,7 @@
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
@@ -30627,12 +30664,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -30724,7 +30761,7 @@
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
@@ -30744,7 +30781,7 @@
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
@@ -30786,12 +30823,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -30872,7 +30909,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>country:AU-TAS:national</t>
+          <t>country:AU-SA:national</t>
         </is>
       </c>
       <c r="AD160" t="inlineStr">
@@ -30958,7 +30995,7 @@
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
@@ -30978,7 +31015,7 @@
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
@@ -31020,12 +31057,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -31117,7 +31154,7 @@
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
@@ -31137,7 +31174,7 @@
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
@@ -31179,12 +31216,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -31265,7 +31302,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>country:AU-VIC:national</t>
+          <t>country:AU-TAS:national</t>
         </is>
       </c>
       <c r="AD162" t="inlineStr">
@@ -31351,7 +31388,7 @@
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
@@ -31371,7 +31408,7 @@
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
@@ -31413,12 +31450,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -31510,7 +31547,7 @@
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
@@ -31530,7 +31567,7 @@
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
@@ -31572,12 +31609,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -31658,7 +31695,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>country:AU-WA:national</t>
+          <t>country:AU-VIC:national</t>
         </is>
       </c>
       <c r="AD164" t="inlineStr">
@@ -31744,7 +31781,7 @@
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
@@ -31764,7 +31801,7 @@
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
@@ -31806,12 +31843,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -31845,81 +31882,95 @@
         </is>
       </c>
       <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT165" t="n">
         <v>1</v>
       </c>
-      <c r="O165" t="n">
-        <v>1</v>
-      </c>
-      <c r="R165" t="n">
-        <v>0.001937969923792046</v>
-      </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP165" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr"/>
-      <c r="AT165" t="n">
-        <v>0</v>
-      </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -31946,123 +31997,512 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>Syphilis congenital</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>country:AU-WA:national</t>
+        </is>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital syphilis notifications.</t>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN166" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
+      <c r="F167" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr">
+      <c r="G167" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
         <is>
           <t>先天性梅毒</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
+      <c r="K167" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr">
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>1</v>
+      </c>
+      <c r="O167" t="n">
+        <v>1</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr"/>
+      <c r="AT167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M166" t="inlineStr">
+      <c r="M168" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N166" t="n">
-        <v>0</v>
-      </c>
-      <c r="O166" t="n">
-        <v>0</v>
-      </c>
-      <c r="R166" t="n">
-        <v>0</v>
-      </c>
-      <c r="S166" t="inlineStr">
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO166" t="inlineStr">
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP166" t="inlineStr">
+      <c r="AP168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR166" t="inlineStr">
+      <c r="AR168" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS166" t="inlineStr"/>
-      <c r="AT166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU166" t="inlineStr">
+      <c r="AS168" t="inlineStr"/>
+      <c r="AT168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU168" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV166" t="inlineStr">
+      <c r="AV168" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW166" t="inlineStr">
+      <c r="AW168" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX166" t="inlineStr">
+      <c r="AX168" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY166" t="inlineStr">
+      <c r="AY168" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ166" t="inlineStr">
+      <c r="AZ168" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA166" t="inlineStr">
+      <c r="BA168" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB166" t="inlineStr">
+      <c r="BB168" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC166" t="inlineStr">
+      <c r="BC168" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -32184,7 +32624,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10">
@@ -32194,7 +32634,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11">
@@ -32214,7 +32654,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -32246,7 +32686,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d167/2026-2029.xlsx
+++ b/diseases/d167/2026-2029.xlsx
@@ -32275,13 +32275,13 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R167" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d167/2026-2029.xlsx
+++ b/diseases/d167/2026-2029.xlsx
@@ -32275,13 +32275,13 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d167/2026-2029.xlsx
+++ b/diseases/d167/2026-2029.xlsx
@@ -4992,11 +4992,6 @@
       <c r="R32" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
@@ -5014,12 +5009,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -5029,11 +5019,6 @@
       </c>
       <c r="AT32" t="n">
         <v>1</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5099,17 +5084,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-OR</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Oregon, United States</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5156,89 +5141,11 @@
           <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Syphilis, Congenital</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>Syphilis, Congenital</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN33" t="b">
-        <v>1</v>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -5246,12 +5153,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -5262,11 +5164,6 @@
       <c r="AT33" t="n">
         <v>1</v>
       </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV33" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5279,32 +5176,32 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5233,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>US-OR</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Oregon, United States</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5366,36 +5263,31 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>1</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1</v>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -5405,65 +5297,55 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AT34" t="n">
         <v>1</v>
       </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -5490,17 +5372,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>US-OR</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Oregon, United States</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5525,177 +5407,89 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Syphilis, Congenital</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Syphilis, Congenital</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>country:US-OR:national</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN35" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AT35" t="n">
         <v>1</v>
       </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -5727,12 +5521,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5786,7 +5580,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
@@ -5809,7 +5603,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -5829,7 +5623,7 @@
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
@@ -5871,12 +5665,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5908,15 +5702,6 @@
         <is>
           <t>2026-04</t>
         </is>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -5953,7 +5738,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -5973,7 +5758,7 @@
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
@@ -6015,12 +5800,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -6097,7 +5882,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -6117,7 +5902,7 @@
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
@@ -6159,12 +5944,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6232,7 +6017,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -6252,7 +6037,7 @@
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
@@ -6294,12 +6079,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6376,7 +6161,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -6396,7 +6181,7 @@
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
@@ -6438,12 +6223,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -6475,6 +6260,15 @@
         <is>
           <t>2026-04</t>
         </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -6511,7 +6305,7 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -6531,7 +6325,7 @@
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
@@ -6573,12 +6367,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6612,18 +6406,10 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -6632,7 +6418,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
@@ -6640,27 +6426,23 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS42" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
+      <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -6670,17 +6452,17 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
@@ -6717,12 +6499,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6756,18 +6538,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
+        <v>0.001937969923792046</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -6776,7 +6553,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
@@ -6784,52 +6561,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS43" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
+      <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -6861,12 +6634,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6891,7 +6664,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -6905,14 +6678,25 @@
       <c r="O44" t="n">
         <v>1</v>
       </c>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
@@ -6920,48 +6704,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS44" t="inlineStr"/>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+        </is>
+      </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -6993,12 +6781,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US-MT</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Montana, United States</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7023,7 +6811,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -7037,17 +6825,22 @@
       <c r="O45" t="n">
         <v>1</v>
       </c>
-      <c r="R45" t="n">
-        <v>0.001937969923792046</v>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+        </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
@@ -7055,48 +6848,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS45" t="inlineStr"/>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+        </is>
+      </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7128,12 +6925,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7158,39 +6955,31 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -7200,65 +6989,55 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AT46" t="n">
         <v>1</v>
       </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -7285,17 +7064,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7320,177 +7099,89 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>1</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Syphilis, Congenital</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>Syphilis, Congenital</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG47" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN47" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ47" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AT47" t="n">
         <v>1</v>
       </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -7522,12 +7213,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>US-MT</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Montana, United States</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7552,104 +7243,89 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>1</v>
-      </c>
-      <c r="P48" t="n">
-        <v>1</v>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ48" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AT48" t="n">
         <v>1</v>
       </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -7676,17 +7352,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>US-MT</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Montana, United States</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7711,177 +7387,80 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="N49" t="n">
-        <v>1</v>
-      </c>
-      <c r="O49" t="n">
-        <v>1</v>
-      </c>
-      <c r="P49" t="n">
-        <v>1</v>
+          <t>2026-05</t>
+        </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Syphilis, Congenital</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>Syphilis, Congenital</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>country:US-MT:national</t>
-        </is>
-      </c>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG49" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN49" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ49" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AT49" t="n">
         <v>1</v>
       </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -7913,12 +7492,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7972,7 +7551,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
@@ -7995,7 +7574,7 @@
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
@@ -8015,7 +7594,7 @@
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
@@ -8057,12 +7636,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -8139,7 +7718,7 @@
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
@@ -8159,7 +7738,7 @@
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
@@ -8201,12 +7780,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8238,15 +7817,6 @@
         <is>
           <t>2026-05</t>
         </is>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -8283,7 +7853,7 @@
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
@@ -8303,7 +7873,7 @@
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
@@ -8345,12 +7915,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8382,6 +7952,15 @@
         <is>
           <t>2026-05</t>
         </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -8418,7 +7997,7 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
@@ -8438,7 +8017,7 @@
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
@@ -8480,12 +8059,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8519,18 +8098,10 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
+        <v>4</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -8539,7 +8110,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
@@ -8547,27 +8118,23 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS54" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
+      <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -8577,17 +8144,17 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
@@ -8624,12 +8191,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8663,18 +8230,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
+        <v>0.003875939847584092</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -8683,7 +8245,7 @@
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
@@ -8691,52 +8253,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS55" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
+      <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8768,12 +8326,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8798,13 +8356,22 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-05</t>
-        </is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -8818,7 +8385,7 @@
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
@@ -8841,12 +8408,12 @@
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -8861,12 +8428,12 @@
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
@@ -8903,12 +8470,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8933,12 +8500,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -8962,7 +8529,7 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
@@ -8985,7 +8552,7 @@
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
@@ -9005,7 +8572,7 @@
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
@@ -9047,12 +8614,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -9077,19 +8644,27 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -9098,7 +8673,7 @@
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
@@ -9106,23 +8681,27 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS58" t="inlineStr"/>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -9132,17 +8711,17 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
@@ -9179,12 +8758,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -9209,22 +8788,27 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>0.003875939847584092</v>
+        <v>0</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -9233,7 +8817,7 @@
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
@@ -9241,48 +8825,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS59" t="inlineStr"/>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
       <c r="AT59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -9314,12 +8902,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9373,7 +8961,7 @@
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
@@ -9396,12 +8984,12 @@
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -9416,12 +9004,12 @@
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
@@ -9458,12 +9046,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9517,7 +9105,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
@@ -9540,7 +9128,7 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
@@ -9560,7 +9148,7 @@
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
@@ -9602,12 +9190,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -9684,7 +9272,7 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
@@ -9704,7 +9292,7 @@
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
@@ -9746,12 +9334,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -9783,15 +9371,6 @@
         <is>
           <t>2026-06</t>
         </is>
-      </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -9828,7 +9407,7 @@
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
@@ -9848,7 +9427,7 @@
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
@@ -9890,12 +9469,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -9972,7 +9551,7 @@
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
@@ -9992,7 +9571,7 @@
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
@@ -10034,12 +9613,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -10078,14 +9657,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10093,7 +9664,7 @@
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
@@ -10101,27 +9672,23 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS65" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
+      <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -10131,17 +9698,17 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
@@ -10178,12 +9745,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -10225,11 +9792,6 @@
       <c r="R66" t="n">
         <v>0</v>
       </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10237,7 +9799,7 @@
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
@@ -10245,52 +9807,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS66" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
+      <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -10322,12 +9880,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -10352,7 +9910,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -10360,19 +9918,31 @@
           <t>2026-06</t>
         </is>
       </c>
+      <c r="N67" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
@@ -10382,7 +9952,7 @@
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
         </is>
       </c>
       <c r="AT67" t="n">
@@ -10390,42 +9960,42 @@
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -10457,12 +10027,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>US-MT</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Montana, United States</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -10487,7 +10057,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -10496,27 +10066,27 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
@@ -10526,7 +10096,7 @@
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
         </is>
       </c>
       <c r="AT68" t="n">
@@ -10534,42 +10104,42 @@
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -10601,12 +10171,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -10631,12 +10201,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -10645,6 +10215,14 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10652,7 +10230,7 @@
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
@@ -10660,23 +10238,27 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS69" t="inlineStr"/>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
       <c r="AT69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -10686,17 +10268,17 @@
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
@@ -10733,12 +10315,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -10763,12 +10345,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -10780,6 +10362,11 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10787,7 +10374,7 @@
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
@@ -10795,48 +10382,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS70" t="inlineStr"/>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
       <c r="AT70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10868,12 +10459,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -10898,107 +10489,89 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>1</v>
-      </c>
-      <c r="P71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ71" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AT71" t="n">
         <v>1</v>
       </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11025,17 +10598,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -11060,177 +10633,89 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>1</v>
-      </c>
-      <c r="P72" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Syphilis, Congenital</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>Syphilis, Congenital</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD72" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE72" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG72" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN72" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AT72" t="n">
         <v>1</v>
       </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11262,12 +10747,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>US-MT</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Montana, United States</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -11292,104 +10777,89 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>1</v>
-      </c>
-      <c r="P73" t="n">
-        <v>1</v>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AT73" t="n">
         <v>1</v>
       </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11416,17 +10886,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>US-MT</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Montana, United States</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11451,177 +10921,89 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>1</v>
-      </c>
-      <c r="P74" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Syphilis, Congenital</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>Syphilis, Congenital</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>country:US-MT:national</t>
-        </is>
-      </c>
-      <c r="AD74" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE74" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF74" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG74" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN74" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ74" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AT74" t="n">
         <v>1</v>
       </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11653,12 +11035,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -11712,7 +11094,7 @@
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
@@ -11735,12 +11117,12 @@
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -11755,12 +11137,12 @@
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
@@ -11797,12 +11179,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -11856,7 +11238,7 @@
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
@@ -11879,7 +11261,7 @@
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
@@ -11899,7 +11281,7 @@
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
@@ -11941,12 +11323,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -12023,7 +11405,7 @@
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
@@ -12043,7 +11425,7 @@
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
@@ -12085,12 +11467,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -12124,18 +11506,10 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
@@ -12144,7 +11518,7 @@
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
@@ -12152,27 +11526,23 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS78" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
+      <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -12182,17 +11552,17 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
@@ -12229,12 +11599,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -12268,18 +11638,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
+        <v>0.005813909771376137</v>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
@@ -12288,7 +11653,7 @@
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
@@ -12296,52 +11661,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS79" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
+      <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -12373,12 +11734,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -12403,7 +11764,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -12412,27 +11773,30 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
@@ -12442,7 +11806,7 @@
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
         </is>
       </c>
       <c r="AT80" t="n">
@@ -12450,42 +11814,42 @@
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -12517,12 +11881,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>US-MT</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Montana, United States</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -12547,7 +11911,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -12556,27 +11920,27 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P81" t="n">
+        <v>1</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
@@ -12586,7 +11950,7 @@
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
         </is>
       </c>
       <c r="AT81" t="n">
@@ -12594,42 +11958,42 @@
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12661,12 +12025,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -12691,12 +12055,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -12720,7 +12084,7 @@
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
@@ -12743,12 +12107,12 @@
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -12763,12 +12127,12 @@
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
@@ -12805,12 +12169,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -12835,12 +12199,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N83" t="n">
@@ -12864,7 +12228,7 @@
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
@@ -12887,7 +12251,7 @@
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
@@ -12907,7 +12271,7 @@
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
@@ -12949,12 +12313,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -12979,19 +12343,27 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
@@ -13000,7 +12372,7 @@
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
@@ -13008,23 +12380,27 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS84" t="inlineStr"/>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
       <c r="AT84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -13034,17 +12410,17 @@
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
@@ -13081,12 +12457,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -13111,22 +12487,27 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>0.005813909771376137</v>
+        <v>0</v>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
@@ -13135,7 +12516,7 @@
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
@@ -13143,48 +12524,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS85" t="inlineStr"/>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13216,12 +12601,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -13246,107 +12631,89 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>1</v>
-      </c>
-      <c r="P86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ86" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AT86" t="n">
         <v>1</v>
       </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13373,17 +12740,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -13408,177 +12775,89 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>1</v>
-      </c>
-      <c r="P87" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Syphilis, Congenital</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>Syphilis, Congenital</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD87" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE87" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF87" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG87" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN87" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ87" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AT87" t="n">
         <v>1</v>
       </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13610,12 +12889,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>US-MT</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Montana, United States</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -13640,104 +12919,89 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>1</v>
-      </c>
-      <c r="P88" t="n">
-        <v>1</v>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ88" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AT88" t="n">
         <v>1</v>
       </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13764,17 +13028,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>US-MT</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Montana, United States</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -13799,177 +13063,89 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>1</v>
-      </c>
-      <c r="P89" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Syphilis, Congenital</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>Syphilis, Congenital</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>country:US-MT:national</t>
-        </is>
-      </c>
-      <c r="AD89" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE89" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF89" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG89" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN89" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ89" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
         </is>
       </c>
       <c r="AT89" t="n">
         <v>1</v>
       </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14001,12 +13177,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -14060,7 +13236,7 @@
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
@@ -14083,12 +13259,12 @@
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -14103,12 +13279,12 @@
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
@@ -14145,12 +13321,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -14189,14 +13365,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="R91" t="n">
-        <v>0</v>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14204,7 +13372,7 @@
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
@@ -14212,27 +13380,23 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS91" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
+      <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -14242,17 +13406,17 @@
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
@@ -14289,12 +13453,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -14336,11 +13500,6 @@
       <c r="R92" t="n">
         <v>0</v>
       </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14348,7 +13507,7 @@
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
@@ -14356,52 +13515,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS92" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
+      <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -14433,12 +13588,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -14463,22 +13618,22 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -14492,7 +13647,7 @@
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
@@ -14515,12 +13670,12 @@
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -14535,12 +13690,12 @@
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
@@ -14577,12 +13732,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -14607,12 +13762,12 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N94" t="n">
@@ -14636,7 +13791,7 @@
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
@@ -14659,7 +13814,7 @@
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
@@ -14679,7 +13834,7 @@
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
@@ -14721,12 +13876,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -14751,22 +13906,13 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="N95" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="R95" t="n">
-        <v>0</v>
+          <t>2026-09</t>
+        </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -14803,7 +13949,7 @@
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
@@ -14823,7 +13969,7 @@
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
@@ -14865,12 +14011,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -14895,12 +14041,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N96" t="n">
@@ -14947,7 +14093,7 @@
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
@@ -14967,7 +14113,7 @@
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
@@ -15009,12 +14155,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -15039,22 +14185,13 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="N97" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" t="n">
-        <v>0</v>
-      </c>
-      <c r="R97" t="n">
-        <v>0</v>
+          <t>2026-09</t>
+        </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -15091,7 +14228,7 @@
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
@@ -15111,7 +14248,7 @@
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
@@ -15153,12 +14290,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -15183,12 +14320,12 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N98" t="n">
@@ -15235,7 +14372,7 @@
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
@@ -15255,7 +14392,7 @@
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
@@ -15297,12 +14434,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -15327,12 +14464,12 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N99" t="n">
@@ -15341,6 +14478,14 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15348,7 +14493,7 @@
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
@@ -15356,23 +14501,27 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS99" t="inlineStr"/>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
       <c r="AT99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -15382,17 +14531,17 @@
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
@@ -15429,12 +14578,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -15459,12 +14608,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N100" t="n">
@@ -15476,6 +14625,11 @@
       <c r="R100" t="n">
         <v>0</v>
       </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15483,7 +14637,7 @@
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
@@ -15491,48 +14645,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS100" t="inlineStr"/>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
       <c r="AT100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15564,12 +14722,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -15603,13 +14761,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>0.00367281181951979</v>
+        <v>0</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -15623,7 +14781,7 @@
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
@@ -15646,12 +14804,12 @@
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -15666,12 +14824,12 @@
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
@@ -15708,12 +14866,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -15747,18 +14905,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
+        <v>0.001937969923792046</v>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
@@ -15767,7 +14920,7 @@
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
@@ -15775,52 +14928,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS102" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
+      <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -15852,12 +15001,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -15882,7 +15031,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -15890,19 +15039,31 @@
           <t>2026-09</t>
         </is>
       </c>
+      <c r="N103" t="n">
+        <v>1</v>
+      </c>
+      <c r="O103" t="n">
+        <v>1</v>
+      </c>
+      <c r="P103" t="n">
+        <v>1</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
@@ -15912,7 +15073,7 @@
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
         </is>
       </c>
       <c r="AT103" t="n">
@@ -15920,42 +15081,42 @@
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -15987,12 +15148,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>US-MT</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Montana, United States</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -16017,7 +15178,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -16026,27 +15187,27 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
-      </c>
-      <c r="R104" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P104" t="n">
+        <v>1</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
@@ -16056,7 +15217,7 @@
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
         </is>
       </c>
       <c r="AT104" t="n">
@@ -16064,42 +15225,42 @@
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16131,12 +15292,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -16161,18 +15322,22 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="U105" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
@@ -16181,7 +15346,7 @@
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
@@ -16189,1681 +15354,46 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS105" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
+      <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>congenital-syphilis</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>AU-SA</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>South Australia, Australia</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>先天性梅毒</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="N106" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0</v>
-      </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP106" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
-      <c r="AT106" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV106" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AW106" t="inlineStr">
-        <is>
-          <t>Australia NINDSS — South Australia</t>
-        </is>
-      </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="BA106" t="inlineStr">
-        <is>
-          <t>Australia NINDSS — South Australia</t>
-        </is>
-      </c>
-      <c r="BB106" t="inlineStr">
-        <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
-        </is>
-      </c>
-      <c r="BC106" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>congenital-syphilis</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>AU-TAS</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Tasmania, Australia</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>先天性梅毒</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="N107" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" t="n">
-        <v>0</v>
-      </c>
-      <c r="R107" t="n">
-        <v>0</v>
-      </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP107" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
-      <c r="AT107" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV107" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AW107" t="inlineStr">
-        <is>
-          <t>Australia NINDSS — Tasmania</t>
-        </is>
-      </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="BA107" t="inlineStr">
-        <is>
-          <t>Australia NINDSS — Tasmania</t>
-        </is>
-      </c>
-      <c r="BB107" t="inlineStr">
-        <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
-        </is>
-      </c>
-      <c r="BC107" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>congenital-syphilis</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>AU-VIC</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Victoria, Australia</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>先天性梅毒</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="N108" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="R108" t="n">
-        <v>0</v>
-      </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP108" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
-      <c r="AT108" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV108" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AW108" t="inlineStr">
-        <is>
-          <t>Australia NINDSS — Victoria</t>
-        </is>
-      </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="BA108" t="inlineStr">
-        <is>
-          <t>Australia NINDSS — Victoria</t>
-        </is>
-      </c>
-      <c r="BB108" t="inlineStr">
-        <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
-        </is>
-      </c>
-      <c r="BC108" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>congenital-syphilis</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>AU-WA</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Western Australia, Australia</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>先天性梅毒</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="N109" t="n">
-        <v>0</v>
-      </c>
-      <c r="O109" t="n">
-        <v>0</v>
-      </c>
-      <c r="R109" t="n">
-        <v>0</v>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP109" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
-        </is>
-      </c>
-      <c r="AT109" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV109" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AW109" t="inlineStr">
-        <is>
-          <t>Australia NINDSS — Western Australia</t>
-        </is>
-      </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="BA109" t="inlineStr">
-        <is>
-          <t>Australia NINDSS — Western Australia</t>
-        </is>
-      </c>
-      <c r="BB109" t="inlineStr">
-        <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
-        </is>
-      </c>
-      <c r="BC109" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>congenital-syphilis</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>先天性梅毒</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="N110" t="n">
-        <v>1</v>
-      </c>
-      <c r="O110" t="n">
-        <v>1</v>
-      </c>
-      <c r="R110" t="n">
-        <v>0.001937969923792046</v>
-      </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP110" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr"/>
-      <c r="AT110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV110" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW110" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA110" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB110" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC110" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>congenital-syphilis</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>先天性梅毒</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="N111" t="n">
-        <v>1</v>
-      </c>
-      <c r="O111" t="n">
-        <v>1</v>
-      </c>
-      <c r="P111" t="n">
-        <v>1</v>
-      </c>
-      <c r="R111" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
-        </is>
-      </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP111" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ111" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr">
-        <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
-        </is>
-      </c>
-      <c r="AT111" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV111" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW111" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>nndss_api; nhss_hiv</t>
-        </is>
-      </c>
-      <c r="BA111" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
-        </is>
-      </c>
-      <c r="BB111" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
-        </is>
-      </c>
-      <c r="BC111" t="inlineStr">
-        <is>
-          <t>api; api</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>congenital-syphilis</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>先天性梅毒</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="N112" t="n">
-        <v>1</v>
-      </c>
-      <c r="O112" t="n">
-        <v>1</v>
-      </c>
-      <c r="P112" t="n">
-        <v>1</v>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
-        </is>
-      </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>Syphilis, Congenital</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>Syphilis, Congenital</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD112" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF112" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG112" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN112" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP112" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr">
-        <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
-        </is>
-      </c>
-      <c r="AT112" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV112" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW112" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>nndss_api; nhss_hiv</t>
-        </is>
-      </c>
-      <c r="BA112" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
-        </is>
-      </c>
-      <c r="BB112" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
-        </is>
-      </c>
-      <c r="BC112" t="inlineStr">
-        <is>
-          <t>api; api</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>congenital-syphilis</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>US-MT</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Montana, United States</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>先天性梅毒</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="N113" t="n">
-        <v>1</v>
-      </c>
-      <c r="O113" t="n">
-        <v>1</v>
-      </c>
-      <c r="P113" t="n">
-        <v>1</v>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U113" t="inlineStr">
-        <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
-        </is>
-      </c>
-      <c r="AA113" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP113" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ113" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr">
-        <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
-        </is>
-      </c>
-      <c r="AT113" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV113" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW113" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="BA113" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="BB113" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="BC113" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>congenital-syphilis</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>US-MT</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Montana, United States</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>先天性梅毒</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="N114" t="n">
-        <v>1</v>
-      </c>
-      <c r="O114" t="n">
-        <v>1</v>
-      </c>
-      <c r="P114" t="n">
-        <v>1</v>
-      </c>
-      <c r="U114" t="inlineStr">
-        <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
-        </is>
-      </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>Syphilis, Congenital</t>
-        </is>
-      </c>
-      <c r="W114" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X114" t="inlineStr">
-        <is>
-          <t>Syphilis, Congenital</t>
-        </is>
-      </c>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA114" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>country:US-MT:national</t>
-        </is>
-      </c>
-      <c r="AD114" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE114" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF114" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG114" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN114" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP114" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ114" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr">
-        <is>
-          <t>HOLD_US_0ad6c8153ae4f9b33fa3f3d4d26d</t>
-        </is>
-      </c>
-      <c r="AT114" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV114" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW114" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="AY114" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="BA114" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="BB114" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="BC114" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>congenital-syphilis</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>先天性梅毒</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="N115" t="n">
-        <v>0</v>
-      </c>
-      <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="R115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP115" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr"/>
-      <c r="AT115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV115" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW115" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA115" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB115" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC115" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -17995,7 +15525,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
@@ -18015,7 +15545,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -18025,7 +15555,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d167/2026-2029.xlsx
+++ b/diseases/d167/2026-2029.xlsx
@@ -15292,108 +15292,252 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>D167</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>Congenital syphilis</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
         <is>
           <t>先天性梅毒</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N105" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" t="n">
-        <v>0</v>
-      </c>
-      <c r="R105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA105" t="inlineStr">
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AO105" t="inlineStr">
+      <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP105" t="inlineStr">
+      <c r="AP106" t="inlineStr">
         <is>
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS105" t="inlineStr"/>
-      <c r="AT105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV105" t="inlineStr">
+      <c r="AS106" t="inlineStr"/>
+      <c r="AT106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV106" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW105" t="inlineStr">
+      <c r="AW106" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
+      <c r="AX106" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY105" t="inlineStr">
+      <c r="AY106" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
+      <c r="AZ106" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA105" t="inlineStr">
+      <c r="BA106" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB105" t="inlineStr">
+      <c r="BB106" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC105" t="inlineStr">
+      <c r="BC106" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -15515,7 +15659,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10">
@@ -15525,7 +15669,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d167/2026-2029.xlsx
+++ b/diseases/d167/2026-2029.xlsx
@@ -1908,6 +1908,11 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1920,12 +1925,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -3309,6 +3324,11 @@
       <c r="O20" t="n">
         <v>1</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3321,12 +3341,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -4719,6 +4749,11 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4731,12 +4766,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -6411,6 +6456,11 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6423,12 +6473,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -8103,6 +8163,11 @@
       <c r="O54" t="n">
         <v>4</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8115,12 +8180,22 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -9657,6 +9732,11 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9669,12 +9749,22 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -11511,6 +11601,11 @@
       <c r="O78" t="n">
         <v>2</v>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11523,12 +11618,22 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -13365,6 +13470,11 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13377,12 +13487,22 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
